--- a/docs/StructureDefinition-AdverseEvent-twltc.xlsx
+++ b/docs/StructureDefinition-AdverseEvent-twltc.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-28T05:34:23+08:00</t>
+    <t>2026-02-28T07:16:04+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-AdverseEvent-twltc.xlsx
+++ b/docs/StructureDefinition-AdverseEvent-twltc.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-28T07:16:04+08:00</t>
+    <t>2026-02-28T23:13:53+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-AdverseEvent-twltc.xlsx
+++ b/docs/StructureDefinition-AdverseEvent-twltc.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AL$72</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AL$75</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2467" uniqueCount="390">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2566" uniqueCount="405">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.4.1</t>
+    <t>1.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-28T23:13:53+08:00</t>
+    <t>2026-03-01T19:25:35+08:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>此 Profile 說明本 IG 如何進一步定義 FHIR 的 AdverseEvent Resource，以呈現失智症個案異常事件警報的資料，包括事件類型、嚴重程度、發生時間、位置等資訊。</t>
+    <t>此 Profile 說明本 IG 如何進一步定義 FHIR 的 AdverseEvent Resource，以呈現長照個案異常事件的資料，包括事件類型、嚴重程度、發生時間、位置、通報方式、多段文字描述與關聯案件等資訊。同時適用於失智照顧及 SDK 異常服務通報場景。</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -417,33 +417,86 @@
     <t>AdverseEvent.extension</t>
   </si>
   <si>
+    <t xml:space="preserve">Extension
+</t>
+  </si>
+  <si>
+    <t>Extension</t>
+  </si>
+  <si>
+    <t>An Extension</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>DomainResource.extension</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
+    <t>AdverseEvent.extension:notifMethod</t>
+  </si>
+  <si>
+    <t>notifMethod</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://ltc-ig.fhir.tw/StructureDefinition/Ext-TW-LTC-AdverseEvent-NotifMethod}
+</t>
+  </si>
+  <si>
+    <t>通報方式（如電話、機構通報等）</t>
+  </si>
+  <si>
+    <t>記錄異常事件的通報方式（如電話、機構通報、LINE 等）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
+    <t>AdverseEvent.extension:description</t>
+  </si>
+  <si>
+    <t>description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://ltc-ig.fhir.tw/StructureDefinition/Ext-TW-LTC-AdverseEvent-Description}
+</t>
+  </si>
+  <si>
+    <t>多段文字描述（事件描述、過程、處理、建議）</t>
+  </si>
+  <si>
+    <t>記錄異常事件的多段文字描述，包含事件描述、發生過程、後續處理、改善建議等</t>
+  </si>
+  <si>
+    <t>AdverseEvent.extension:about</t>
+  </si>
+  <si>
+    <t>about</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://ltc-ig.fhir.tw/StructureDefinition/Ext-TW-LTC-AdverseEvent-About}
+</t>
+  </si>
+  <si>
+    <t>關聯的案件（EpisodeOfCare）或照顧計畫（CarePlan）</t>
+  </si>
+  <si>
+    <t>AdverseEvent.modifierExtension</t>
+  </si>
+  <si>
     <t>extensions
 user content</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension
-</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
-    <t>DomainResource.extension</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
-  </si>
-  <si>
-    <t>AdverseEvent.modifierExtension</t>
-  </si>
-  <si>
     <t>Extensions that cannot be ignored</t>
   </si>
   <si>
@@ -451,6 +504,9 @@
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+  </si>
+  <si>
     <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
   </si>
   <si>
@@ -498,17 +554,13 @@
     <t>AdverseEvent.identifier.extension</t>
   </si>
   <si>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
     <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
   </si>
   <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
     <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
   </si>
   <si>
     <t>Element.extension</t>
@@ -706,13 +758,7 @@
     <t>This element defines the specific type of event that occurred or that was prevented from occurring.</t>
   </si>
   <si>
-    <t>example</t>
-  </si>
-  <si>
-    <t>Detailed type of event.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/adverse-event-type|4.0.1</t>
+    <t>http://ltc-ig.fhir.tw/ValueSet/vs-tw-ltc-incident-category</t>
   </si>
   <si>
     <t>FiveWs.what[x]</t>
@@ -1013,6 +1059,9 @@
   </si>
   <si>
     <t>Assessment whether this event was of real importance.</t>
+  </si>
+  <si>
+    <t>example</t>
   </si>
   <si>
     <t>Overall seriousness of this event for the patient.</t>
@@ -1547,7 +1596,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AL72"/>
+  <dimension ref="A1:AL75"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="46.7109375" customWidth="true" bestFit="true"/>
@@ -2466,7 +2515,7 @@
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>129</v>
+        <v>20</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -2485,17 +2534,15 @@
         <v>20</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="L9" t="s" s="2">
         <v>130</v>
       </c>
-      <c r="L9" t="s" s="2">
+      <c r="M9" t="s" s="2">
         <v>131</v>
       </c>
-      <c r="M9" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="N9" t="s" s="2">
-        <v>133</v>
-      </c>
+      <c r="N9" s="2"/>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
         <v>20</v>
@@ -2532,16 +2579,14 @@
         <v>20</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC9" t="s" s="2">
-        <v>20</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="AC9" s="2"/>
       <c r="AD9" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>20</v>
+        <v>133</v>
       </c>
       <c r="AF9" t="s" s="2">
         <v>134</v>
@@ -2562,19 +2607,21 @@
         <v>20</v>
       </c>
       <c r="AL9" t="s" s="2">
-        <v>127</v>
+        <v>20</v>
       </c>
     </row>
-    <row r="10" hidden="true">
+    <row r="10">
       <c r="A10" t="s" s="2">
         <v>136</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="C10" s="2"/>
+        <v>128</v>
+      </c>
+      <c r="C10" t="s" s="2">
+        <v>137</v>
+      </c>
       <c r="D10" t="s" s="2">
-        <v>129</v>
+        <v>20</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
@@ -2584,29 +2631,25 @@
         <v>77</v>
       </c>
       <c r="H10" t="s" s="2">
-        <v>20</v>
+        <v>85</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>85</v>
+        <v>20</v>
       </c>
       <c r="J10" t="s" s="2">
         <v>20</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="N10" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="O10" t="s" s="2">
-        <v>139</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="N10" s="2"/>
+      <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
         <v>20</v>
       </c>
@@ -2654,7 +2697,7 @@
         <v>20</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>76</v>
@@ -2663,7 +2706,7 @@
         <v>77</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>20</v>
+        <v>141</v>
       </c>
       <c r="AJ10" t="s" s="2">
         <v>135</v>
@@ -2672,17 +2715,19 @@
         <v>20</v>
       </c>
       <c r="AL10" t="s" s="2">
-        <v>127</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="C11" s="2"/>
+        <v>128</v>
+      </c>
+      <c r="C11" t="s" s="2">
+        <v>143</v>
+      </c>
       <c r="D11" t="s" s="2">
         <v>20</v>
       </c>
@@ -2691,7 +2736,7 @@
         <v>76</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>85</v>
@@ -2700,23 +2745,19 @@
         <v>20</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>85</v>
+        <v>20</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="N11" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="O11" t="s" s="2">
         <v>146</v>
       </c>
+      <c r="N11" s="2"/>
+      <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
         <v>20</v>
       </c>
@@ -2764,19 +2805,19 @@
         <v>20</v>
       </c>
       <c r="AF11" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="AG11" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH11" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI11" t="s" s="2">
         <v>141</v>
       </c>
-      <c r="AG11" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH11" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI11" t="s" s="2">
-        <v>20</v>
-      </c>
       <c r="AJ11" t="s" s="2">
-        <v>96</v>
+        <v>135</v>
       </c>
       <c r="AK11" t="s" s="2">
         <v>20</v>
@@ -2785,14 +2826,16 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12" hidden="true">
+    <row r="12">
       <c r="A12" t="s" s="2">
         <v>147</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>147</v>
-      </c>
-      <c r="C12" s="2"/>
+        <v>128</v>
+      </c>
+      <c r="C12" t="s" s="2">
+        <v>148</v>
+      </c>
       <c r="D12" t="s" s="2">
         <v>20</v>
       </c>
@@ -2801,10 +2844,10 @@
         <v>76</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>20</v>
+        <v>85</v>
       </c>
       <c r="I12" t="s" s="2">
         <v>20</v>
@@ -2813,10 +2856,10 @@
         <v>20</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="M12" t="s" s="2">
         <v>150</v>
@@ -2870,37 +2913,37 @@
         <v>20</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>151</v>
+        <v>134</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>20</v>
+        <v>141</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>20</v>
+        <v>135</v>
       </c>
       <c r="AK12" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>152</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>129</v>
+        <v>152</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
@@ -2913,24 +2956,26 @@
         <v>20</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>20</v>
+        <v>85</v>
       </c>
       <c r="J13" t="s" s="2">
         <v>20</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>131</v>
+        <v>153</v>
       </c>
       <c r="M13" t="s" s="2">
         <v>154</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="O13" s="2"/>
+        <v>155</v>
+      </c>
+      <c r="O13" t="s" s="2">
+        <v>156</v>
+      </c>
       <c r="P13" t="s" s="2">
         <v>20</v>
       </c>
@@ -2966,19 +3011,19 @@
         <v>20</v>
       </c>
       <c r="AB13" t="s" s="2">
-        <v>155</v>
+        <v>20</v>
       </c>
       <c r="AC13" t="s" s="2">
-        <v>156</v>
+        <v>20</v>
       </c>
       <c r="AD13" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE13" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF13" t="s" s="2">
         <v>157</v>
-      </c>
-      <c r="AF13" t="s" s="2">
-        <v>158</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>76</v>
@@ -2996,15 +3041,15 @@
         <v>20</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>152</v>
+        <v>127</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3021,13 +3066,13 @@
         <v>85</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>85</v>
+        <v>20</v>
       </c>
       <c r="J14" t="s" s="2">
         <v>85</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>104</v>
+        <v>159</v>
       </c>
       <c r="L14" t="s" s="2">
         <v>160</v>
@@ -3049,7 +3094,7 @@
         <v>20</v>
       </c>
       <c r="S14" t="s" s="2">
-        <v>164</v>
+        <v>20</v>
       </c>
       <c r="T14" t="s" s="2">
         <v>20</v>
@@ -3064,13 +3109,13 @@
         <v>20</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>165</v>
+        <v>20</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>166</v>
+        <v>20</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>167</v>
+        <v>20</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>20</v>
@@ -3088,7 +3133,7 @@
         <v>20</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>76</v>
@@ -3106,15 +3151,15 @@
         <v>20</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>169</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3134,23 +3179,19 @@
         <v>20</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>85</v>
+        <v>20</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="O15" t="s" s="2">
-        <v>175</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="N15" s="2"/>
+      <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>20</v>
       </c>
@@ -3174,13 +3215,13 @@
         <v>20</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>176</v>
+        <v>20</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>177</v>
+        <v>20</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>178</v>
+        <v>20</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>20</v>
@@ -3198,7 +3239,7 @@
         <v>20</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>179</v>
+        <v>168</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>76</v>
@@ -3210,7 +3251,7 @@
         <v>20</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>96</v>
+        <v>20</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>20</v>
@@ -3219,48 +3260,46 @@
         <v>169</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>20</v>
+        <v>152</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>85</v>
+        <v>20</v>
       </c>
       <c r="I16" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>85</v>
+        <v>20</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>98</v>
+        <v>129</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="O16" t="s" s="2">
-        <v>184</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>20</v>
       </c>
@@ -3272,7 +3311,7 @@
         <v>20</v>
       </c>
       <c r="T16" t="s" s="2">
-        <v>185</v>
+        <v>20</v>
       </c>
       <c r="U16" t="s" s="2">
         <v>20</v>
@@ -3296,45 +3335,45 @@
         <v>20</v>
       </c>
       <c r="AB16" t="s" s="2">
-        <v>20</v>
+        <v>132</v>
       </c>
       <c r="AC16" t="s" s="2">
-        <v>20</v>
+        <v>173</v>
       </c>
       <c r="AD16" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE16" t="s" s="2">
-        <v>20</v>
+        <v>133</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>186</v>
+        <v>174</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>96</v>
+        <v>135</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>187</v>
+        <v>169</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>188</v>
+        <v>175</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>188</v>
+        <v>175</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3342,7 +3381,7 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="G17" t="s" s="2">
         <v>84</v>
@@ -3351,24 +3390,26 @@
         <v>85</v>
       </c>
       <c r="I17" t="s" s="2">
-        <v>20</v>
+        <v>85</v>
       </c>
       <c r="J17" t="s" s="2">
         <v>85</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>148</v>
+        <v>104</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>189</v>
+        <v>176</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>190</v>
+        <v>177</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="O17" s="2"/>
+        <v>178</v>
+      </c>
+      <c r="O17" t="s" s="2">
+        <v>179</v>
+      </c>
       <c r="P17" t="s" s="2">
         <v>20</v>
       </c>
@@ -3377,10 +3418,10 @@
         <v>20</v>
       </c>
       <c r="S17" t="s" s="2">
-        <v>20</v>
+        <v>180</v>
       </c>
       <c r="T17" t="s" s="2">
-        <v>192</v>
+        <v>20</v>
       </c>
       <c r="U17" t="s" s="2">
         <v>20</v>
@@ -3392,13 +3433,13 @@
         <v>20</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>20</v>
+        <v>181</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>20</v>
+        <v>182</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>20</v>
+        <v>183</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>20</v>
@@ -3416,7 +3457,7 @@
         <v>20</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>76</v>
@@ -3434,15 +3475,15 @@
         <v>20</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>194</v>
+        <v>185</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3465,16 +3506,20 @@
         <v>85</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="N18" s="2"/>
-      <c r="O18" s="2"/>
+        <v>189</v>
+      </c>
+      <c r="N18" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="O18" t="s" s="2">
+        <v>191</v>
+      </c>
       <c r="P18" t="s" s="2">
         <v>20</v>
       </c>
@@ -3498,13 +3543,13 @@
         <v>20</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>20</v>
+        <v>192</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>20</v>
+        <v>193</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>20</v>
+        <v>194</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>20</v>
@@ -3522,7 +3567,7 @@
         <v>20</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>76</v>
@@ -3540,15 +3585,15 @@
         <v>20</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>200</v>
+        <v>185</v>
       </c>
     </row>
-    <row r="19" hidden="true">
+    <row r="19">
       <c r="A19" t="s" s="2">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3556,13 +3601,13 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="G19" t="s" s="2">
         <v>84</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>20</v>
+        <v>85</v>
       </c>
       <c r="I19" t="s" s="2">
         <v>20</v>
@@ -3571,18 +3616,20 @@
         <v>85</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>202</v>
+        <v>98</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="O19" s="2"/>
+        <v>199</v>
+      </c>
+      <c r="O19" t="s" s="2">
+        <v>200</v>
+      </c>
       <c r="P19" t="s" s="2">
         <v>20</v>
       </c>
@@ -3594,7 +3641,7 @@
         <v>20</v>
       </c>
       <c r="T19" t="s" s="2">
-        <v>20</v>
+        <v>201</v>
       </c>
       <c r="U19" t="s" s="2">
         <v>20</v>
@@ -3630,7 +3677,7 @@
         <v>20</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>76</v>
@@ -3648,15 +3695,15 @@
         <v>20</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>207</v>
+        <v>203</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3673,21 +3720,23 @@
         <v>85</v>
       </c>
       <c r="I20" t="s" s="2">
-        <v>85</v>
+        <v>20</v>
       </c>
       <c r="J20" t="s" s="2">
         <v>85</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>104</v>
+        <v>165</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="N20" s="2"/>
+        <v>206</v>
+      </c>
+      <c r="N20" t="s" s="2">
+        <v>207</v>
+      </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>20</v>
@@ -3700,7 +3749,7 @@
         <v>20</v>
       </c>
       <c r="T20" t="s" s="2">
-        <v>20</v>
+        <v>208</v>
       </c>
       <c r="U20" t="s" s="2">
         <v>20</v>
@@ -3712,13 +3761,13 @@
         <v>20</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>165</v>
+        <v>20</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>211</v>
+        <v>20</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>212</v>
+        <v>20</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>20</v>
@@ -3736,10 +3785,10 @@
         <v>20</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AH20" t="s" s="2">
         <v>84</v>
@@ -3751,18 +3800,18 @@
         <v>96</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>213</v>
+        <v>20</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>20</v>
+        <v>210</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3773,7 +3822,7 @@
         <v>76</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>20</v>
@@ -3785,13 +3834,13 @@
         <v>85</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>171</v>
+        <v>212</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3818,13 +3867,13 @@
         <v>20</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>176</v>
+        <v>20</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>217</v>
+        <v>20</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>218</v>
+        <v>20</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>20</v>
@@ -3842,13 +3891,13 @@
         <v>20</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>20</v>
@@ -3857,18 +3906,18 @@
         <v>96</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>213</v>
+        <v>20</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>20</v>
+        <v>216</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3882,7 +3931,7 @@
         <v>84</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>85</v>
+        <v>20</v>
       </c>
       <c r="I22" t="s" s="2">
         <v>20</v>
@@ -3891,15 +3940,17 @@
         <v>85</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>171</v>
+        <v>218</v>
       </c>
       <c r="L22" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="M22" t="s" s="2">
         <v>220</v>
       </c>
-      <c r="M22" t="s" s="2">
+      <c r="N22" t="s" s="2">
         <v>221</v>
       </c>
-      <c r="N22" s="2"/>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>20</v>
@@ -3924,31 +3975,31 @@
         <v>20</v>
       </c>
       <c r="X22" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y22" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z22" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA22" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB22" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC22" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD22" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE22" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF22" t="s" s="2">
         <v>222</v>
-      </c>
-      <c r="Y22" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="Z22" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="AA22" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB22" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC22" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD22" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE22" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF22" t="s" s="2">
-        <v>219</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>76</v>
@@ -3963,18 +4014,18 @@
         <v>96</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>225</v>
+        <v>20</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>20</v>
+        <v>223</v>
       </c>
     </row>
-    <row r="23" hidden="true">
+    <row r="23">
       <c r="A23" t="s" s="2">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3982,28 +4033,28 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="G23" t="s" s="2">
         <v>84</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>20</v>
+        <v>85</v>
       </c>
       <c r="I23" t="s" s="2">
-        <v>20</v>
+        <v>85</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>20</v>
+        <v>85</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>148</v>
+        <v>104</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>149</v>
+        <v>225</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>150</v>
+        <v>226</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -4030,13 +4081,13 @@
         <v>20</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>20</v>
+        <v>181</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>20</v>
+        <v>227</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>20</v>
+        <v>228</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>20</v>
@@ -4054,10 +4105,10 @@
         <v>20</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>151</v>
+        <v>224</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AH23" t="s" s="2">
         <v>84</v>
@@ -4066,25 +4117,25 @@
         <v>20</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>20</v>
+        <v>96</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>20</v>
+        <v>229</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>152</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>129</v>
+        <v>20</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -4100,20 +4151,18 @@
         <v>20</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>20</v>
+        <v>85</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>130</v>
+        <v>187</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>131</v>
+        <v>231</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>133</v>
-      </c>
+        <v>232</v>
+      </c>
+      <c r="N24" s="2"/>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>20</v>
@@ -4138,31 +4187,31 @@
         <v>20</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>20</v>
+        <v>192</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>20</v>
+        <v>233</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>20</v>
+        <v>234</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>155</v>
+        <v>20</v>
       </c>
       <c r="AC24" t="s" s="2">
-        <v>156</v>
+        <v>20</v>
       </c>
       <c r="AD24" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>157</v>
+        <v>20</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>158</v>
+        <v>230</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>76</v>
@@ -4174,21 +4223,21 @@
         <v>20</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>135</v>
+        <v>96</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>20</v>
+        <v>229</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>152</v>
+        <v>20</v>
       </c>
     </row>
-    <row r="25" hidden="true">
+    <row r="25">
       <c r="A25" t="s" s="2">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4199,10 +4248,10 @@
         <v>76</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>20</v>
+        <v>85</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>20</v>
@@ -4211,20 +4260,16 @@
         <v>85</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>229</v>
+        <v>187</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>233</v>
-      </c>
+        <v>237</v>
+      </c>
+      <c r="N25" s="2"/>
+      <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>20</v>
       </c>
@@ -4248,13 +4293,11 @@
         <v>20</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y25" t="s" s="2">
-        <v>20</v>
-      </c>
+        <v>192</v>
+      </c>
+      <c r="Y25" s="2"/>
       <c r="Z25" t="s" s="2">
-        <v>20</v>
+        <v>238</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>20</v>
@@ -4272,13 +4315,13 @@
         <v>20</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>20</v>
@@ -4287,18 +4330,18 @@
         <v>96</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>20</v>
+        <v>239</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>235</v>
+        <v>20</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4306,35 +4349,31 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="G26" t="s" s="2">
         <v>84</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>85</v>
+        <v>20</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>85</v>
+        <v>20</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>148</v>
+        <v>165</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>237</v>
+        <v>166</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>240</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="N26" s="2"/>
+      <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>20</v>
       </c>
@@ -4382,69 +4421,67 @@
         <v>20</v>
       </c>
       <c r="AF26" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="AG26" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH26" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI26" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ26" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AK26" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL26" t="s" s="2">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="27" hidden="true">
+      <c r="A27" t="s" s="2">
         <v>241</v>
       </c>
-      <c r="AG26" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH26" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI26" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ26" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="AK26" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL26" t="s" s="2">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="s" s="2">
-        <v>243</v>
-      </c>
       <c r="B27" t="s" s="2">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>244</v>
+        <v>152</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>85</v>
+        <v>20</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>85</v>
+        <v>20</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>245</v>
+        <v>129</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>246</v>
+        <v>171</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>247</v>
+        <v>172</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>249</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>20</v>
       </c>
@@ -4480,45 +4517,45 @@
         <v>20</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>20</v>
+        <v>132</v>
       </c>
       <c r="AC27" t="s" s="2">
-        <v>20</v>
+        <v>173</v>
       </c>
       <c r="AD27" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>20</v>
+        <v>133</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>243</v>
+        <v>174</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>96</v>
+        <v>135</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>250</v>
+        <v>20</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>20</v>
+        <v>169</v>
       </c>
     </row>
-    <row r="28" hidden="true">
+    <row r="28">
       <c r="A28" t="s" s="2">
-        <v>251</v>
+        <v>242</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>251</v>
+        <v>242</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4529,28 +4566,32 @@
         <v>76</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>20</v>
+        <v>85</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>20</v>
+        <v>85</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>148</v>
+        <v>243</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>149</v>
+        <v>244</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="N28" s="2"/>
-      <c r="O28" s="2"/>
+        <v>245</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="O28" t="s" s="2">
+        <v>247</v>
+      </c>
       <c r="P28" t="s" s="2">
         <v>20</v>
       </c>
@@ -4598,67 +4639,69 @@
         <v>20</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>151</v>
+        <v>248</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>20</v>
+        <v>96</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>152</v>
+        <v>249</v>
       </c>
     </row>
-    <row r="29" hidden="true">
+    <row r="29">
       <c r="A29" t="s" s="2">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>129</v>
+        <v>20</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>20</v>
+        <v>85</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>20</v>
+        <v>85</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>130</v>
+        <v>165</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>131</v>
+        <v>251</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>154</v>
+        <v>252</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="O29" s="2"/>
+        <v>253</v>
+      </c>
+      <c r="O29" t="s" s="2">
+        <v>254</v>
+      </c>
       <c r="P29" t="s" s="2">
         <v>20</v>
       </c>
@@ -4694,49 +4737,49 @@
         <v>20</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>155</v>
+        <v>20</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>156</v>
+        <v>20</v>
       </c>
       <c r="AD29" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>157</v>
+        <v>20</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>158</v>
+        <v>255</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>135</v>
+        <v>96</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>152</v>
+        <v>256</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>20</v>
+        <v>258</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -4755,18 +4798,20 @@
         <v>85</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>148</v>
+        <v>259</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="O30" s="2"/>
+        <v>262</v>
+      </c>
+      <c r="O30" t="s" s="2">
+        <v>263</v>
+      </c>
       <c r="P30" t="s" s="2">
         <v>20</v>
       </c>
@@ -4817,30 +4862,30 @@
         <v>257</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AH30" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>258</v>
+        <v>20</v>
       </c>
       <c r="AJ30" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>20</v>
+        <v>264</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>127</v>
+        <v>20</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4860,20 +4905,18 @@
         <v>20</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>85</v>
+        <v>20</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>98</v>
+        <v>165</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>260</v>
+        <v>166</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>262</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="N31" s="2"/>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>20</v>
@@ -4898,13 +4941,13 @@
         <v>20</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>176</v>
+        <v>20</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>263</v>
+        <v>20</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>264</v>
+        <v>20</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>20</v>
@@ -4922,7 +4965,7 @@
         <v>20</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>265</v>
+        <v>168</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>76</v>
@@ -4934,13 +4977,13 @@
         <v>20</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>96</v>
+        <v>20</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>127</v>
+        <v>169</v>
       </c>
     </row>
     <row r="32" hidden="true">
@@ -4952,14 +4995,14 @@
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>20</v>
+        <v>152</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>20</v>
@@ -4968,19 +5011,19 @@
         <v>20</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>85</v>
+        <v>20</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>142</v>
+        <v>129</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>267</v>
+        <v>171</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>268</v>
+        <v>172</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>269</v>
+        <v>155</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5018,45 +5061,45 @@
         <v>20</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>20</v>
+        <v>132</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>20</v>
+        <v>173</v>
       </c>
       <c r="AD32" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>20</v>
+        <v>133</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>270</v>
+        <v>174</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>96</v>
+        <v>135</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>271</v>
+        <v>169</v>
       </c>
     </row>
-    <row r="33" hidden="true">
+    <row r="33">
       <c r="A33" t="s" s="2">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5064,13 +5107,13 @@
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="G33" t="s" s="2">
         <v>84</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>20</v>
+        <v>85</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>20</v>
@@ -5079,16 +5122,16 @@
         <v>85</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>148</v>
+        <v>165</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5138,7 +5181,7 @@
         <v>20</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>76</v>
@@ -5147,7 +5190,7 @@
         <v>84</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>20</v>
+        <v>272</v>
       </c>
       <c r="AJ33" t="s" s="2">
         <v>96</v>
@@ -5161,10 +5204,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5187,16 +5230,16 @@
         <v>85</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>278</v>
+        <v>98</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -5222,13 +5265,13 @@
         <v>20</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>20</v>
+        <v>192</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>20</v>
+        <v>277</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>20</v>
+        <v>278</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>20</v>
@@ -5246,7 +5289,7 @@
         <v>20</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>76</v>
@@ -5261,18 +5304,18 @@
         <v>96</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>282</v>
+        <v>20</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>20</v>
+        <v>127</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5280,13 +5323,13 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="G35" t="s" s="2">
         <v>84</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>85</v>
+        <v>20</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>20</v>
@@ -5295,15 +5338,17 @@
         <v>85</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>284</v>
+        <v>159</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="N35" s="2"/>
+        <v>282</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>283</v>
+      </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>20</v>
@@ -5352,7 +5397,7 @@
         <v>20</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>76</v>
@@ -5367,18 +5412,18 @@
         <v>96</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>287</v>
+        <v>20</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>20</v>
+        <v>285</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5392,7 +5437,7 @@
         <v>84</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>85</v>
+        <v>20</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>20</v>
@@ -5401,15 +5446,17 @@
         <v>85</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>284</v>
+        <v>165</v>
       </c>
       <c r="L36" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="M36" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="N36" t="s" s="2">
         <v>289</v>
       </c>
-      <c r="M36" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="N36" s="2"/>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>20</v>
@@ -5458,7 +5505,7 @@
         <v>20</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>76</v>
@@ -5476,10 +5523,10 @@
         <v>20</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>20</v>
+        <v>127</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
         <v>291</v>
       </c>
@@ -5492,13 +5539,13 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="G37" t="s" s="2">
         <v>84</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>85</v>
+        <v>20</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>20</v>
@@ -5507,16 +5554,16 @@
         <v>85</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -5581,7 +5628,7 @@
         <v>96</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>20</v>
@@ -5589,10 +5636,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5600,10 +5647,10 @@
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>85</v>
@@ -5615,13 +5662,13 @@
         <v>85</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5672,13 +5719,13 @@
         <v>20</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>20</v>
@@ -5687,18 +5734,18 @@
         <v>96</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>20</v>
+        <v>301</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="39" hidden="true">
+    <row r="39">
       <c r="A39" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5712,22 +5759,22 @@
         <v>84</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>20</v>
+        <v>85</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>20</v>
+        <v>85</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>148</v>
+        <v>298</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>149</v>
+        <v>303</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>150</v>
+        <v>304</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5778,7 +5825,7 @@
         <v>20</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>151</v>
+        <v>302</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>76</v>
@@ -5790,53 +5837,53 @@
         <v>20</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>20</v>
+        <v>96</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>152</v>
+        <v>20</v>
       </c>
     </row>
-    <row r="40" hidden="true">
+    <row r="40">
       <c r="A40" t="s" s="2">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>129</v>
+        <v>20</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>20</v>
+        <v>85</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>20</v>
+        <v>85</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>130</v>
+        <v>298</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>131</v>
+        <v>306</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>154</v>
+        <v>307</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>133</v>
+        <v>308</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -5874,45 +5921,45 @@
         <v>20</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>155</v>
+        <v>20</v>
       </c>
       <c r="AC40" t="s" s="2">
-        <v>156</v>
+        <v>20</v>
       </c>
       <c r="AD40" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>157</v>
+        <v>20</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>158</v>
+        <v>305</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>135</v>
+        <v>96</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>20</v>
+        <v>309</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>152</v>
+        <v>20</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5920,10 +5967,10 @@
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>85</v>
@@ -5935,17 +5982,15 @@
         <v>85</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>148</v>
+        <v>311</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>303</v>
+        <v>312</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>256</v>
-      </c>
+        <v>313</v>
+      </c>
+      <c r="N41" s="2"/>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>20</v>
@@ -5994,16 +6039,16 @@
         <v>20</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>257</v>
+        <v>310</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>258</v>
+        <v>20</v>
       </c>
       <c r="AJ41" t="s" s="2">
         <v>96</v>
@@ -6012,15 +6057,15 @@
         <v>20</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>127</v>
+        <v>20</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>304</v>
+        <v>314</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>304</v>
+        <v>314</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6040,20 +6085,18 @@
         <v>20</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>85</v>
+        <v>20</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>98</v>
+        <v>165</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>260</v>
+        <v>166</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>262</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="N42" s="2"/>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>20</v>
@@ -6078,13 +6121,13 @@
         <v>20</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>176</v>
+        <v>20</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>263</v>
+        <v>20</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>264</v>
+        <v>20</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>20</v>
@@ -6102,7 +6145,7 @@
         <v>20</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>265</v>
+        <v>168</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>76</v>
@@ -6114,32 +6157,32 @@
         <v>20</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>96</v>
+        <v>20</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>127</v>
+        <v>169</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>305</v>
+        <v>315</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>305</v>
+        <v>315</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>20</v>
+        <v>152</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>20</v>
@@ -6148,19 +6191,19 @@
         <v>20</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>85</v>
+        <v>20</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>142</v>
+        <v>129</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>267</v>
+        <v>171</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>268</v>
+        <v>172</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>269</v>
+        <v>155</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6198,45 +6241,45 @@
         <v>20</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>20</v>
+        <v>132</v>
       </c>
       <c r="AC43" t="s" s="2">
-        <v>20</v>
+        <v>173</v>
       </c>
       <c r="AD43" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>20</v>
+        <v>133</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>270</v>
+        <v>174</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>96</v>
+        <v>135</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>271</v>
+        <v>169</v>
       </c>
     </row>
-    <row r="44" hidden="true">
+    <row r="44">
       <c r="A44" t="s" s="2">
-        <v>306</v>
+        <v>316</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>306</v>
+        <v>316</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6244,13 +6287,13 @@
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="G44" t="s" s="2">
         <v>84</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>20</v>
+        <v>85</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>20</v>
@@ -6259,16 +6302,16 @@
         <v>85</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>148</v>
+        <v>165</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>273</v>
+        <v>317</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -6318,7 +6361,7 @@
         <v>20</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>76</v>
@@ -6327,7 +6370,7 @@
         <v>84</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>20</v>
+        <v>272</v>
       </c>
       <c r="AJ44" t="s" s="2">
         <v>96</v>
@@ -6339,12 +6382,12 @@
         <v>127</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>307</v>
+        <v>318</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>307</v>
+        <v>318</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6358,7 +6401,7 @@
         <v>84</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>85</v>
+        <v>20</v>
       </c>
       <c r="I45" t="s" s="2">
         <v>20</v>
@@ -6367,15 +6410,17 @@
         <v>85</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>308</v>
+        <v>98</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>309</v>
+        <v>274</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>310</v>
-      </c>
-      <c r="N45" s="2"/>
+        <v>275</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>276</v>
+      </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>20</v>
@@ -6400,13 +6445,13 @@
         <v>20</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>20</v>
+        <v>192</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>20</v>
+        <v>277</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>20</v>
+        <v>278</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>20</v>
@@ -6424,7 +6469,7 @@
         <v>20</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>307</v>
+        <v>279</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>76</v>
@@ -6442,15 +6487,15 @@
         <v>20</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>20</v>
+        <v>127</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6470,18 +6515,20 @@
         <v>20</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>20</v>
+        <v>85</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>148</v>
+        <v>159</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>149</v>
+        <v>281</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="N46" s="2"/>
+        <v>282</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>283</v>
+      </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>20</v>
@@ -6530,7 +6577,7 @@
         <v>20</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>151</v>
+        <v>284</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>76</v>
@@ -6542,32 +6589,32 @@
         <v>20</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>20</v>
+        <v>96</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>152</v>
+        <v>285</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>129</v>
+        <v>20</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>20</v>
@@ -6576,19 +6623,19 @@
         <v>20</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>20</v>
+        <v>85</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>130</v>
+        <v>165</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>131</v>
+        <v>287</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>154</v>
+        <v>288</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>133</v>
+        <v>289</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -6626,45 +6673,45 @@
         <v>20</v>
       </c>
       <c r="AB47" t="s" s="2">
-        <v>155</v>
+        <v>20</v>
       </c>
       <c r="AC47" t="s" s="2">
-        <v>156</v>
+        <v>20</v>
       </c>
       <c r="AD47" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>157</v>
+        <v>20</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>158</v>
+        <v>290</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>135</v>
+        <v>96</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>152</v>
+        <v>127</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6672,7 +6719,7 @@
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="G48" t="s" s="2">
         <v>84</v>
@@ -6687,17 +6734,15 @@
         <v>85</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>148</v>
+        <v>322</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>314</v>
+        <v>323</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>256</v>
-      </c>
+        <v>324</v>
+      </c>
+      <c r="N48" s="2"/>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>20</v>
@@ -6746,7 +6791,7 @@
         <v>20</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>257</v>
+        <v>321</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>76</v>
@@ -6755,7 +6800,7 @@
         <v>84</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>258</v>
+        <v>20</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>96</v>
@@ -6764,15 +6809,15 @@
         <v>20</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>127</v>
+        <v>20</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>315</v>
+        <v>325</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>315</v>
+        <v>325</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6792,20 +6837,18 @@
         <v>20</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>85</v>
+        <v>20</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>98</v>
+        <v>165</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>260</v>
+        <v>166</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>262</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="N49" s="2"/>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>20</v>
@@ -6830,13 +6873,13 @@
         <v>20</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>176</v>
+        <v>20</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>263</v>
+        <v>20</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>264</v>
+        <v>20</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>20</v>
@@ -6854,7 +6897,7 @@
         <v>20</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>265</v>
+        <v>168</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>76</v>
@@ -6866,32 +6909,32 @@
         <v>20</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>96</v>
+        <v>20</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>127</v>
+        <v>169</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>316</v>
+        <v>326</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>316</v>
+        <v>326</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>20</v>
+        <v>152</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>20</v>
@@ -6900,19 +6943,19 @@
         <v>20</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>85</v>
+        <v>20</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>142</v>
+        <v>129</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>267</v>
+        <v>171</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>268</v>
+        <v>172</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>269</v>
+        <v>155</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -6950,45 +6993,45 @@
         <v>20</v>
       </c>
       <c r="AB50" t="s" s="2">
-        <v>20</v>
+        <v>132</v>
       </c>
       <c r="AC50" t="s" s="2">
-        <v>20</v>
+        <v>173</v>
       </c>
       <c r="AD50" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE50" t="s" s="2">
-        <v>20</v>
+        <v>133</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>270</v>
+        <v>174</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>96</v>
+        <v>135</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>271</v>
+        <v>169</v>
       </c>
     </row>
-    <row r="51" hidden="true">
+    <row r="51">
       <c r="A51" t="s" s="2">
-        <v>317</v>
+        <v>327</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>317</v>
+        <v>327</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -6996,13 +7039,13 @@
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="G51" t="s" s="2">
         <v>84</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>20</v>
+        <v>85</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>20</v>
@@ -7011,16 +7054,16 @@
         <v>85</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>148</v>
+        <v>165</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>273</v>
+        <v>328</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -7070,7 +7113,7 @@
         <v>20</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>76</v>
@@ -7079,7 +7122,7 @@
         <v>84</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>20</v>
+        <v>272</v>
       </c>
       <c r="AJ51" t="s" s="2">
         <v>96</v>
@@ -7091,12 +7134,12 @@
         <v>127</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>318</v>
+        <v>329</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>318</v>
+        <v>329</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7110,7 +7153,7 @@
         <v>84</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>85</v>
+        <v>20</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>20</v>
@@ -7119,15 +7162,17 @@
         <v>85</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>171</v>
+        <v>98</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>319</v>
+        <v>274</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>320</v>
-      </c>
-      <c r="N52" s="2"/>
+        <v>275</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>276</v>
+      </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>20</v>
@@ -7152,13 +7197,13 @@
         <v>20</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>222</v>
+        <v>192</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>321</v>
+        <v>277</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>322</v>
+        <v>278</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>20</v>
@@ -7176,7 +7221,7 @@
         <v>20</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>318</v>
+        <v>279</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>76</v>
@@ -7194,15 +7239,15 @@
         <v>20</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>20</v>
+        <v>127</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7216,7 +7261,7 @@
         <v>84</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>85</v>
+        <v>20</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>20</v>
@@ -7225,15 +7270,17 @@
         <v>85</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>324</v>
+        <v>281</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="N53" s="2"/>
+        <v>282</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>283</v>
+      </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>20</v>
@@ -7258,13 +7305,13 @@
         <v>20</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>165</v>
+        <v>20</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>326</v>
+        <v>20</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>327</v>
+        <v>20</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>20</v>
@@ -7282,7 +7329,7 @@
         <v>20</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>323</v>
+        <v>284</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>76</v>
@@ -7300,15 +7347,15 @@
         <v>20</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>20</v>
+        <v>285</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7322,7 +7369,7 @@
         <v>84</v>
       </c>
       <c r="H54" t="s" s="2">
-        <v>85</v>
+        <v>20</v>
       </c>
       <c r="I54" t="s" s="2">
         <v>20</v>
@@ -7331,15 +7378,17 @@
         <v>85</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>329</v>
+        <v>287</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="N54" s="2"/>
+        <v>288</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>289</v>
+      </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>20</v>
@@ -7364,13 +7413,13 @@
         <v>20</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>165</v>
+        <v>20</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>331</v>
+        <v>20</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>332</v>
+        <v>20</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>20</v>
@@ -7388,7 +7437,7 @@
         <v>20</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>328</v>
+        <v>290</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>76</v>
@@ -7406,15 +7455,15 @@
         <v>20</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>20</v>
+        <v>127</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7437,13 +7486,13 @@
         <v>85</v>
       </c>
       <c r="K55" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="L55" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="M55" t="s" s="2">
         <v>334</v>
-      </c>
-      <c r="L55" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>336</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -7470,13 +7519,13 @@
         <v>20</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>20</v>
+        <v>335</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>20</v>
+        <v>336</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>20</v>
+        <v>337</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>20</v>
@@ -7494,7 +7543,7 @@
         <v>20</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>76</v>
@@ -7509,7 +7558,7 @@
         <v>96</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>337</v>
+        <v>20</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>20</v>
@@ -7543,13 +7592,13 @@
         <v>85</v>
       </c>
       <c r="K56" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="L56" t="s" s="2">
         <v>339</v>
       </c>
-      <c r="L56" t="s" s="2">
+      <c r="M56" t="s" s="2">
         <v>340</v>
-      </c>
-      <c r="M56" t="s" s="2">
-        <v>341</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -7576,13 +7625,13 @@
         <v>20</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>20</v>
+        <v>181</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>20</v>
+        <v>341</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>20</v>
+        <v>342</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>20</v>
@@ -7606,7 +7655,7 @@
         <v>76</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>20</v>
@@ -7621,12 +7670,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="57" hidden="true">
+    <row r="57">
       <c r="A57" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7637,10 +7686,10 @@
         <v>76</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H57" t="s" s="2">
-        <v>20</v>
+        <v>85</v>
       </c>
       <c r="I57" t="s" s="2">
         <v>20</v>
@@ -7649,7 +7698,7 @@
         <v>85</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>343</v>
+        <v>187</v>
       </c>
       <c r="L57" t="s" s="2">
         <v>344</v>
@@ -7682,13 +7731,13 @@
         <v>20</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>20</v>
+        <v>181</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>20</v>
+        <v>346</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>20</v>
+        <v>347</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>20</v>
@@ -7706,13 +7755,13 @@
         <v>20</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>20</v>
@@ -7727,12 +7776,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="58" hidden="true">
+    <row r="58">
       <c r="A58" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -7746,22 +7795,22 @@
         <v>84</v>
       </c>
       <c r="H58" t="s" s="2">
-        <v>20</v>
+        <v>85</v>
       </c>
       <c r="I58" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>20</v>
+        <v>85</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>148</v>
+        <v>349</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>149</v>
+        <v>350</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>150</v>
+        <v>351</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -7812,7 +7861,7 @@
         <v>20</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>151</v>
+        <v>348</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>76</v>
@@ -7824,25 +7873,25 @@
         <v>20</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>20</v>
+        <v>96</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>20</v>
+        <v>352</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>152</v>
+        <v>20</v>
       </c>
     </row>
-    <row r="59" hidden="true">
+    <row r="59">
       <c r="A59" t="s" s="2">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>129</v>
+        <v>20</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -7852,26 +7901,24 @@
         <v>77</v>
       </c>
       <c r="H59" t="s" s="2">
-        <v>20</v>
+        <v>85</v>
       </c>
       <c r="I59" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>20</v>
+        <v>85</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>130</v>
+        <v>354</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>131</v>
+        <v>355</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>133</v>
-      </c>
+        <v>356</v>
+      </c>
+      <c r="N59" s="2"/>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>20</v>
@@ -7920,7 +7967,7 @@
         <v>20</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>158</v>
+        <v>353</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>76</v>
@@ -7932,25 +7979,25 @@
         <v>20</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>135</v>
+        <v>96</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>152</v>
+        <v>20</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>348</v>
+        <v>357</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>348</v>
+        <v>357</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>349</v>
+        <v>20</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -7963,26 +8010,22 @@
         <v>20</v>
       </c>
       <c r="I60" t="s" s="2">
-        <v>85</v>
+        <v>20</v>
       </c>
       <c r="J60" t="s" s="2">
         <v>85</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>130</v>
+        <v>358</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>350</v>
+        <v>359</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>139</v>
-      </c>
+        <v>360</v>
+      </c>
+      <c r="N60" s="2"/>
+      <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>20</v>
       </c>
@@ -8030,7 +8073,7 @@
         <v>20</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>76</v>
@@ -8042,29 +8085,29 @@
         <v>20</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>135</v>
+        <v>96</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>127</v>
+        <v>20</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>354</v>
+        <v>20</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="G61" t="s" s="2">
         <v>84</v>
@@ -8076,16 +8119,16 @@
         <v>20</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>85</v>
+        <v>20</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>355</v>
+        <v>165</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>356</v>
+        <v>166</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>357</v>
+        <v>167</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -8136,10 +8179,10 @@
         <v>20</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>353</v>
+        <v>168</v>
       </c>
       <c r="AG61" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AH61" t="s" s="2">
         <v>84</v>
@@ -8148,25 +8191,25 @@
         <v>20</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>96</v>
+        <v>20</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>20</v>
+        <v>169</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>20</v>
+        <v>152</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
@@ -8182,18 +8225,20 @@
         <v>20</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>85</v>
+        <v>20</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>343</v>
+        <v>129</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>359</v>
+        <v>171</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="N62" s="2"/>
+        <v>172</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>155</v>
+      </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>20</v>
@@ -8242,7 +8287,7 @@
         <v>20</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>358</v>
+        <v>174</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>76</v>
@@ -8254,53 +8299,57 @@
         <v>20</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>96</v>
+        <v>135</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>20</v>
+        <v>169</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>20</v>
+        <v>364</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I63" t="s" s="2">
-        <v>20</v>
+        <v>85</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>20</v>
+        <v>85</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>148</v>
+        <v>129</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>149</v>
+        <v>365</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="N63" s="2"/>
-      <c r="O63" s="2"/>
+        <v>366</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="O63" t="s" s="2">
+        <v>156</v>
+      </c>
       <c r="P63" t="s" s="2">
         <v>20</v>
       </c>
@@ -8348,44 +8397,44 @@
         <v>20</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>151</v>
+        <v>367</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>20</v>
+        <v>135</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>152</v>
+        <v>127</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>129</v>
+        <v>369</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>20</v>
@@ -8394,20 +8443,18 @@
         <v>20</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>20</v>
+        <v>85</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>130</v>
+        <v>370</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>131</v>
+        <v>371</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>133</v>
-      </c>
+        <v>372</v>
+      </c>
+      <c r="N64" s="2"/>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>20</v>
@@ -8456,37 +8503,37 @@
         <v>20</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>158</v>
+        <v>368</v>
       </c>
       <c r="AG64" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>135</v>
+        <v>96</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>152</v>
+        <v>20</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>363</v>
+        <v>373</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>363</v>
+        <v>373</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>349</v>
+        <v>20</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
@@ -8499,26 +8546,22 @@
         <v>20</v>
       </c>
       <c r="I65" t="s" s="2">
-        <v>85</v>
+        <v>20</v>
       </c>
       <c r="J65" t="s" s="2">
         <v>85</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>130</v>
+        <v>358</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>350</v>
+        <v>374</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="O65" t="s" s="2">
-        <v>139</v>
-      </c>
+        <v>375</v>
+      </c>
+      <c r="N65" s="2"/>
+      <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>20</v>
       </c>
@@ -8566,7 +8609,7 @@
         <v>20</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>352</v>
+        <v>373</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>76</v>
@@ -8578,21 +8621,21 @@
         <v>20</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>135</v>
+        <v>96</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>127</v>
+        <v>20</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>364</v>
+        <v>376</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>364</v>
+        <v>376</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8612,16 +8655,16 @@
         <v>20</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>85</v>
+        <v>20</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>365</v>
+        <v>166</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>366</v>
+        <v>167</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -8648,13 +8691,13 @@
         <v>20</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>222</v>
+        <v>20</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>367</v>
+        <v>20</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>368</v>
+        <v>20</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>20</v>
@@ -8672,7 +8715,7 @@
         <v>20</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>364</v>
+        <v>168</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>76</v>
@@ -8684,32 +8727,32 @@
         <v>20</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>96</v>
+        <v>20</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>20</v>
+        <v>169</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>369</v>
+        <v>377</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>369</v>
+        <v>377</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>20</v>
+        <v>152</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>20</v>
@@ -8718,18 +8761,20 @@
         <v>20</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>85</v>
+        <v>20</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>148</v>
+        <v>129</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>370</v>
+        <v>171</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="N67" s="2"/>
+        <v>172</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>155</v>
+      </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>20</v>
@@ -8778,65 +8823,69 @@
         <v>20</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>369</v>
+        <v>174</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>96</v>
+        <v>135</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>20</v>
+        <v>169</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>20</v>
+        <v>364</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I68" t="s" s="2">
-        <v>20</v>
+        <v>85</v>
       </c>
       <c r="J68" t="s" s="2">
         <v>85</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>373</v>
+        <v>129</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>374</v>
+        <v>365</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="N68" s="2"/>
-      <c r="O68" s="2"/>
+        <v>366</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="O68" t="s" s="2">
+        <v>156</v>
+      </c>
       <c r="P68" t="s" s="2">
         <v>20</v>
       </c>
@@ -8884,33 +8933,33 @@
         <v>20</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>96</v>
+        <v>135</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>20</v>
+        <v>127</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -8933,13 +8982,13 @@
         <v>85</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>171</v>
+        <v>187</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -8966,31 +9015,31 @@
         <v>20</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>222</v>
+        <v>335</v>
       </c>
       <c r="Y69" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="Z69" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="AA69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF69" t="s" s="2">
         <v>379</v>
-      </c>
-      <c r="Z69" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="AA69" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB69" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC69" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD69" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE69" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF69" t="s" s="2">
-        <v>376</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>76</v>
@@ -9013,10 +9062,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9027,7 +9076,7 @@
         <v>76</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>20</v>
@@ -9039,13 +9088,13 @@
         <v>85</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>382</v>
+        <v>165</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -9096,13 +9145,13 @@
         <v>20</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>20</v>
@@ -9119,10 +9168,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9133,7 +9182,7 @@
         <v>76</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>20</v>
@@ -9145,13 +9194,13 @@
         <v>85</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -9202,13 +9251,13 @@
         <v>20</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>20</v>
@@ -9225,10 +9274,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -9239,7 +9288,7 @@
         <v>76</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>20</v>
@@ -9251,13 +9300,13 @@
         <v>85</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>388</v>
+        <v>187</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -9284,13 +9333,13 @@
         <v>20</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>20</v>
+        <v>335</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>20</v>
+        <v>394</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>20</v>
+        <v>395</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>20</v>
@@ -9308,13 +9357,13 @@
         <v>20</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>20</v>
@@ -9329,8 +9378,326 @@
         <v>20</v>
       </c>
     </row>
+    <row r="73" hidden="true">
+      <c r="A73" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="B73" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="C73" s="2"/>
+      <c r="D73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E73" s="2"/>
+      <c r="F73" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J73" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K73" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="L73" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="M73" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="N73" s="2"/>
+      <c r="O73" s="2"/>
+      <c r="P73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q73" s="2"/>
+      <c r="R73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF73" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="AG73" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ73" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL73" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="74" hidden="true">
+      <c r="A74" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="B74" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="C74" s="2"/>
+      <c r="D74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E74" s="2"/>
+      <c r="F74" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J74" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K74" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="L74" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="M74" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="N74" s="2"/>
+      <c r="O74" s="2"/>
+      <c r="P74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q74" s="2"/>
+      <c r="R74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF74" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="AG74" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ74" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL74" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="75" hidden="true">
+      <c r="A75" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="B75" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="C75" s="2"/>
+      <c r="D75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E75" s="2"/>
+      <c r="F75" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J75" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K75" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="L75" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="M75" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="N75" s="2"/>
+      <c r="O75" s="2"/>
+      <c r="P75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q75" s="2"/>
+      <c r="R75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF75" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="AG75" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ75" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL75" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AL72">
+  <autoFilter ref="A1:AL75">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -9340,7 +9707,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI71">
+  <conditionalFormatting sqref="A2:AI74">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-AdverseEvent-twltc.xlsx
+++ b/docs/StructureDefinition-AdverseEvent-twltc.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-01T19:25:35+08:00</t>
+    <t>2026-03-02T02:26:08+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-AdverseEvent-twltc.xlsx
+++ b/docs/StructureDefinition-AdverseEvent-twltc.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-02T02:26:08+08:00</t>
+    <t>2026-04-02T13:32:15+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-AdverseEvent-twltc.xlsx
+++ b/docs/StructureDefinition-AdverseEvent-twltc.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T13:32:15+08:00</t>
+    <t>2026-04-03T21:17:06+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-AdverseEvent-twltc.xlsx
+++ b/docs/StructureDefinition-AdverseEvent-twltc.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-03T21:17:06+08:00</t>
+    <t>2026-06-25T08:48:04+08:00</t>
   </si>
   <si>
     <t>Publisher</t>
